--- a/input/Studies/MEET2/Dehydrator.xlsx
+++ b/input/Studies/MEET2/Dehydrator.xlsx
@@ -3447,7 +3447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="11.453125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -3525,6 +3525,26 @@
           <t>Model ID</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Glycol Pump Injection Ratio</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Still Vent Controlled Flag</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Stripping Gas Flow Rate</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Tank Flash Controlled Flag</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3572,6 +3592,18 @@
         <is>
           <t>Dehydrator.json</t>
         </is>
+      </c>
+      <c r="M2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="N2" t="b">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
